--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Repository Test Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repository Test Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,11 +647,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-07T22:33:16.887892</t>
+          <t>2026-02-08T00:13:43.346253</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-07T22:33:30.046977</t>
+          <t>2026-02-08T00:13:53.333733</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T00:13:43.346253</t>
+          <t>2026-02-08T00:22:56.505482</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T00:13:53.333733</t>
+          <t>2026-02-08T00:23:07.631633</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T00:22:56.505482</t>
+          <t>2026-02-08T00:43:13.715123</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T00:23:07.631633</t>
+          <t>2026-02-08T00:43:25.242316</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T00:43:13.715123</t>
+          <t>2026-02-08T01:05:46.204669</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="AC2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T00:43:25.242316</t>
+          <t>2026-02-08T01:05:58.132780</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T01:05:46.204669</t>
+          <t>2026-02-08T02:27:19.513461</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T01:05:58.132780</t>
+          <t>2026-02-08T02:27:58.296605</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repository Test Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Repository Test Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T02:27:19.513461</t>
+          <t>2026-02-08T21:11:38.842423</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T02:27:58.296605</t>
+          <t>2026-02-08T21:12:12.279188</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T21:11:38.842423</t>
+          <t>2026-02-08T21:23:07.725616</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T21:12:12.279188</t>
+          <t>2026-02-08T21:23:46.451655</t>
         </is>
       </c>
       <c r="D3" t="n">

--- a/src/test_analysis_report.xlsx
+++ b/src/test_analysis_report.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -445,31 +445,32 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="50" customWidth="1" min="30" max="30"/>
-    <col width="42" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,125 +511,130 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Coverage Report</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Feature Scenarios</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Feature Files</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Perf Tests</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Perf Files</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>E2E Tests</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>E2E Files</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Smoke Tests</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Smoke Files</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total Test Files</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Frameworks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Languages</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Commits</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Commits (30d)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Commits (90d)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Commits (1y)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Commits/Week</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Contributors</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Has CI/CD</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>CI/CD Platform</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Auto Testing</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Security Scan</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Auto Deploy</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Workflows</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Repository URL</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Error Message</t>
         </is>
@@ -647,7 +653,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-08T21:23:07.725616</t>
+          <t>2026-02-08T21:45:56.135679</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -662,15 +668,12 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>87</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -681,27 +684,27 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>6</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>pytest, pytest-bdd</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Python, JavaScript, TypeScript</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
@@ -712,34 +715,37 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.08</v>
       </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="AA2" t="b">
-        <v>1</v>
-      </c>
       <c r="AB2" t="b">
         <v>1</v>
       </c>
       <c r="AC2" t="b">
         <v>1</v>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>test, doc-gen-copilot-sdk, security-reporter-agent, doc-genagent</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://github.com/joeycmlam/mypps.git</t>
         </is>
@@ -758,7 +764,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-08T21:23:46.451655</t>
+          <t>2026-02-08T21:46:42.440877</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -773,14 +779,11 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -800,49 +803,52 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.08</v>
       </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA3" t="b">
-        <v>0</v>
-      </c>
       <c r="AB3" t="b">
         <v>0</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://github.com/joeycmlam/mtkdata.git</t>
         </is>
